--- a/public/ctm.xlsx
+++ b/public/ctm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diepm\Desktop\git\diepgia-management\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67C4A75D-DACB-401D-9088-50D30E7885AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B57F549F-7E65-408B-BDDF-D30178A883C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="653" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -47,10 +47,10 @@
     <t>KHỐI LƯỢNG</t>
   </si>
   <si>
-    <t>GIÁ 1KG</t>
+    <t>ĐƠN GIÁ</t>
   </si>
   <si>
-    <t>GIÁ</t>
+    <t>TỔNG TIỀN</t>
   </si>
 </sst>
 </file>
